--- a/astro-site/public/dl/bar-business-plan/bar-opening-checklist.xlsx
+++ b/astro-site/public/dl/bar-business-plan/bar-opening-checklist.xlsx
@@ -643,7 +643,7 @@
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>Bring the name approval, articles of organization and your photo ID</t>
+          <t>Most states let you file online; check the name is available first</t>
         </is>
       </c>
     </row>
@@ -697,7 +697,7 @@
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>Your accountant / bookkeeper picks your NAICS code (722410 drinking places or 722511 full-service restaurant), depending on whether the bar or table service weighs more. It can affect inspections and your liquor license class</t>
+          <t>Your accountant / bookkeeper picks your NAICS code (722410 drinking places or 722511 full-service restaurant), depending on whether the bar or table service weighs more</t>
         </is>
       </c>
     </row>
@@ -1050,7 +1050,7 @@
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>Ask for 2-3 months of rent abatement during the build-out</t>
+          <t>Ask for 2-3 months of rent abatement during the build-out and a liquor license contingency, so rent does not start, or you can exit, if the license is late or denied.</t>
         </is>
       </c>
     </row>
@@ -1479,7 +1479,7 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>2-4 weeks</t>
+          <t>1-3 months</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>Your distributor installs the lines and glycol. Compare distributors (national, regional, craft); tied-house rules limit what a brewer can give you free</t>
+          <t>A draft installer, sometimes arranged through your distributor, installs the lines and glycol; budget it yourself. Compare distributors (national, regional, craft); tied-house rules limit what a brewer can give you free</t>
         </is>
       </c>
     </row>
@@ -1945,7 +1945,7 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>Split shifts (lunch + dinner) or continuous; for a bar, build the schedule around the evening peak and last call</t>
+          <t>Overlapping evening shifts; build the schedule around the after-work rush, the evening peak and last call</t>
         </is>
       </c>
     </row>
@@ -2161,7 +2161,7 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>Pouring and draft service, cocktails and vermouth, small-plates service at the bar; checking IDs and cutting off guests</t>
+          <t>Pouring and draft service, cocktails and wine by the glass, small-plates service at the bar; checking IDs and cutting off guests</t>
         </is>
       </c>
     </row>
@@ -2879,12 +2879,12 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Weekly food cost check</t>
+          <t>Weekly food and pour cost check</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>Kitchen lead</t>
+          <t>Owner + kitchen lead</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
